--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:10:03+00:00</t>
+    <t>2023-03-24T14:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:10:14+00:00</t>
+    <t>2023-03-24T14:14:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:14:45+00:00</t>
+    <t>2023-03-24T14:36:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:36:11+00:00</t>
+    <t>2023-03-24T14:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:36:59+00:00</t>
+    <t>2023-03-24T14:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:42:38+00:00</t>
+    <t>2023-03-24T15:33:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:33:20+00:00</t>
+    <t>2023-03-24T15:33:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:33:53+00:00</t>
+    <t>2023-03-24T15:38:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:38:14+00:00</t>
+    <t>2023-03-26T08:37:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T08:37:00+00:00</t>
+    <t>2023-03-26T08:42:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3390" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3390" uniqueCount="590">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T08:42:47+00:00</t>
+    <t>2023-03-26T09:01:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -817,6 +817,9 @@
   </si>
   <si>
     <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>Lab order number</t>
   </si>
   <si>
     <t>CodeableConcept.text</t>
@@ -5199,7 +5202,7 @@
         <v>77</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>77</v>
+        <v>261</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>77</v>
@@ -5238,7 +5241,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5256,21 +5259,21 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5296,29 +5299,29 @@
         <v>100</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>77</v>
@@ -5354,7 +5357,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5372,21 +5375,21 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5412,13 +5415,13 @@
         <v>157</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5432,7 +5435,7 @@
         <v>77</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>77</v>
@@ -5468,7 +5471,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5486,21 +5489,21 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5523,13 +5526,13 @@
         <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5580,7 +5583,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5598,21 +5601,21 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5635,16 +5638,16 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5694,7 +5697,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5712,21 +5715,21 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5749,17 +5752,17 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5808,7 +5811,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5823,10 +5826,10 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5837,10 +5840,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5866,14 +5869,14 @@
         <v>100</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5922,7 +5925,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5937,10 +5940,10 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5951,10 +5954,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5977,13 +5980,13 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6034,7 +6037,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6049,10 +6052,10 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -6063,10 +6066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6092,14 +6095,14 @@
         <v>144</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -6148,7 +6151,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6163,10 +6166,10 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -6177,10 +6180,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6203,19 +6206,19 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6264,7 +6267,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6279,10 +6282,10 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -6293,10 +6296,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6322,14 +6325,14 @@
         <v>106</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6357,10 +6360,10 @@
         <v>175</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6378,7 +6381,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>86</v>
@@ -6393,13 +6396,13 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6407,10 +6410,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6436,13 +6439,13 @@
         <v>182</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6472,7 +6475,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6490,7 +6493,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6508,7 +6511,7 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -6519,10 +6522,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6631,10 +6634,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6745,10 +6748,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6861,10 +6864,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6909,7 +6912,7 @@
         <v>77</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>77</v>
@@ -6948,7 +6951,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6966,21 +6969,21 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7006,14 +7009,14 @@
         <v>182</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -7038,10 +7041,10 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Z43" t="s" s="2">
         <v>77</v>
@@ -7062,7 +7065,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7080,7 +7083,7 @@
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -7091,10 +7094,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7120,13 +7123,13 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7137,7 +7140,7 @@
         <v>77</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>77</v>
@@ -7155,10 +7158,10 @@
         <v>175</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -7176,7 +7179,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>86</v>
@@ -7191,13 +7194,13 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -7205,10 +7208,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7234,20 +7237,20 @@
         <v>106</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q45" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="R45" t="s" s="2">
         <v>77</v>
@@ -7271,10 +7274,10 @@
         <v>175</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
@@ -7292,7 +7295,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7307,13 +7310,13 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -7321,10 +7324,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7350,13 +7353,13 @@
         <v>182</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7382,13 +7385,13 @@
         <v>77</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>77</v>
@@ -7406,7 +7409,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7421,13 +7424,13 @@
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -7435,10 +7438,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7464,10 +7467,10 @@
         <v>157</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7518,7 +7521,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7536,7 +7539,7 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7547,10 +7550,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7573,19 +7576,19 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7634,7 +7637,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7652,10 +7655,10 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7663,14 +7666,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7689,17 +7692,17 @@
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7748,7 +7751,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7763,13 +7766,13 @@
         <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7777,10 +7780,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7803,17 +7806,17 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7862,7 +7865,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7877,13 +7880,13 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7891,10 +7894,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7917,13 +7920,13 @@
         <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7974,7 +7977,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7989,13 +7992,13 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -8003,14 +8006,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8029,17 +8032,17 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8088,7 +8091,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8097,19 +8100,19 @@
         <v>86</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -8117,14 +8120,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8143,17 +8146,17 @@
         <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -8202,7 +8205,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8211,7 +8214,7 @@
         <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>98</v>
@@ -8220,7 +8223,7 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -8231,10 +8234,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8257,17 +8260,17 @@
         <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8316,7 +8319,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8331,13 +8334,13 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8345,10 +8348,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8374,14 +8377,14 @@
         <v>182</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8409,10 +8412,10 @@
         <v>110</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8430,7 +8433,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8445,13 +8448,13 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8459,14 +8462,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8485,19 +8488,19 @@
         <v>87</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8546,7 +8549,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8561,13 +8564,13 @@
         <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8575,10 +8578,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8601,17 +8604,17 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8660,7 +8663,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8675,13 +8678,13 @@
         <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8689,10 +8692,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8718,13 +8721,13 @@
         <v>182</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8750,10 +8753,10 @@
         <v>77</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z58" t="s" s="2">
         <v>77</v>
@@ -8774,7 +8777,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8789,24 +8792,24 @@
         <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8829,16 +8832,16 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8888,7 +8891,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8903,13 +8906,13 @@
         <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -8917,10 +8920,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8943,13 +8946,13 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9000,7 +9003,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9015,24 +9018,24 @@
         <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9055,13 +9058,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9112,7 +9115,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9127,10 +9130,10 @@
         <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -9141,14 +9144,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9167,16 +9170,16 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9226,7 +9229,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9241,10 +9244,10 @@
         <v>98</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -9255,10 +9258,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9281,17 +9284,17 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9340,7 +9343,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9358,7 +9361,7 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -9369,10 +9372,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9481,10 +9484,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9595,14 +9598,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9624,10 +9627,10 @@
         <v>132</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>135</v>
@@ -9682,7 +9685,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9711,10 +9714,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9737,17 +9740,17 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -9796,7 +9799,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9814,7 +9817,7 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9825,10 +9828,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9851,19 +9854,19 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9912,7 +9915,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9930,7 +9933,7 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9941,10 +9944,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9967,13 +9970,13 @@
         <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10024,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10042,7 +10045,7 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -10053,14 +10056,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10079,17 +10082,17 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -10138,7 +10141,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10156,7 +10159,7 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -10167,10 +10170,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10279,10 +10282,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10393,14 +10396,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10422,10 +10425,10 @@
         <v>132</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>135</v>
@@ -10480,7 +10483,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10509,14 +10512,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10538,16 +10541,16 @@
         <v>182</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -10572,10 +10575,10 @@
         <v>77</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="Z74" t="s" s="2">
         <v>77</v>
@@ -10596,7 +10599,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>86</v>
@@ -10614,7 +10617,7 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -10625,10 +10628,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10651,13 +10654,13 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10708,7 +10711,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>86</v>
@@ -10726,7 +10729,7 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -10737,10 +10740,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10763,17 +10766,17 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -10822,7 +10825,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10840,7 +10843,7 @@
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10851,10 +10854,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10963,10 +10966,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11077,14 +11080,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11106,10 +11109,10 @@
         <v>132</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>135</v>
@@ -11164,7 +11167,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11193,14 +11196,14 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11222,14 +11225,14 @@
         <v>182</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>77</v>
@@ -11254,10 +11257,10 @@
         <v>77</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="Z80" t="s" s="2">
         <v>77</v>
@@ -11278,7 +11281,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>86</v>
@@ -11296,7 +11299,7 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -11307,10 +11310,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11419,10 +11422,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11533,10 +11536,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11649,10 +11652,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11761,10 +11764,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11875,10 +11878,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11991,10 +11994,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12105,10 +12108,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12170,7 +12173,7 @@
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>77</v>
@@ -12217,10 +12220,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12331,10 +12334,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12447,10 +12450,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12495,7 +12498,7 @@
         <v>77</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>77</v>
@@ -12534,7 +12537,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12552,21 +12555,21 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12589,17 +12592,17 @@
         <v>77</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>77</v>
@@ -12636,17 +12639,17 @@
         <v>77</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AC92" s="2"/>
       <c r="AD92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>86</v>
@@ -12664,7 +12667,7 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
@@ -12675,13 +12678,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>77</v>
@@ -12703,17 +12706,17 @@
         <v>77</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
@@ -12762,7 +12765,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>86</v>
@@ -12780,7 +12783,7 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:01:05+00:00</t>
+    <t>2023-03-26T09:02:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:02:01+00:00</t>
+    <t>2023-03-26T09:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:07:12+00:00</t>
+    <t>2023-03-26T10:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:35:39+00:00</t>
+    <t>2023-03-26T10:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:35:51+00:00</t>
+    <t>2023-03-26T10:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:42:59+00:00</t>
+    <t>2023-03-26T11:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:08:41+00:00</t>
+    <t>2023-03-26T11:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:16:53+00:00</t>
+    <t>2023-03-26T11:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:17:47+00:00</t>
+    <t>2023-03-26T11:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:23:31+00:00</t>
+    <t>2023-03-27T11:26:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -9046,7 +9046,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T11:26:57+00:00</t>
+    <t>2023-03-27T11:35:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T11:35:12+00:00</t>
+    <t>2023-03-27T12:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:01:10+00:00</t>
+    <t>2023-03-27T12:02:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:02:15+00:00</t>
+    <t>2023-03-27T12:10:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:10:50+00:00</t>
+    <t>2023-03-28T07:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:37:59+00:00</t>
+    <t>2023-03-28T07:45:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:45:58+00:00</t>
+    <t>2023-03-28T07:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:53:05+00:00</t>
+    <t>2023-03-29T10:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T10:46:03+00:00</t>
+    <t>2023-03-29T10:52:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T10:52:43+00:00</t>
+    <t>2023-03-29T11:10:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T11:10:06+00:00</t>
+    <t>2023-03-31T13:54:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T13:54:07+00:00</t>
+    <t>2023-03-31T13:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T13:55:03+00:00</t>
+    <t>2023-04-01T08:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:28:06+00:00</t>
+    <t>2023-04-01T08:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:29:12+00:00</t>
+    <t>2023-04-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:49:37+00:00</t>
+    <t>2023-04-01T08:50:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:50:39+00:00</t>
+    <t>2023-04-03T05:56:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T05:56:04+00:00</t>
+    <t>2023-04-03T09:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:35:38+00:00</t>
+    <t>2023-04-03T09:37:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:37:11+00:00</t>
+    <t>2023-04-03T09:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$93</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:57:00+00:00</t>
+    <t>2023-04-03T10:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1963,6 +1966,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -2302,7 +2320,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2414,7 +2432,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>85</v>
       </c>
@@ -2528,7 +2546,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>93</v>
       </c>
@@ -2640,7 +2658,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>99</v>
       </c>
@@ -2754,7 +2772,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>105</v>
       </c>
@@ -2868,7 +2886,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>114</v>
       </c>
@@ -2982,7 +3000,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>122</v>
       </c>
@@ -3096,7 +3114,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>130</v>
       </c>
@@ -3210,7 +3228,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>138</v>
       </c>
@@ -3326,7 +3344,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>143</v>
       </c>
@@ -3438,7 +3456,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>153</v>
       </c>
@@ -3552,7 +3570,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>155</v>
       </c>
@@ -3664,7 +3682,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>162</v>
       </c>
@@ -3778,7 +3796,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>169</v>
       </c>
@@ -3894,7 +3912,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>180</v>
       </c>
@@ -4010,7 +4028,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>192</v>
       </c>
@@ -4122,7 +4140,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>194</v>
       </c>
@@ -4236,7 +4254,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>196</v>
       </c>
@@ -4352,7 +4370,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>206</v>
       </c>
@@ -4464,7 +4482,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>208</v>
       </c>
@@ -4578,7 +4596,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>210</v>
       </c>
@@ -4694,7 +4712,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>220</v>
       </c>
@@ -4808,7 +4826,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>228</v>
       </c>
@@ -4922,7 +4940,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>236</v>
       </c>
@@ -5036,7 +5054,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>245</v>
       </c>
@@ -5152,7 +5170,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>255</v>
       </c>
@@ -5268,7 +5286,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>265</v>
       </c>
@@ -5384,7 +5402,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>276</v>
       </c>
@@ -5498,7 +5516,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>285</v>
       </c>
@@ -5610,7 +5628,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>293</v>
       </c>
@@ -5724,7 +5742,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>302</v>
       </c>
@@ -5838,7 +5856,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>309</v>
       </c>
@@ -5952,7 +5970,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>313</v>
       </c>
@@ -6064,7 +6082,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>319</v>
       </c>
@@ -6178,7 +6196,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>325</v>
       </c>
@@ -6294,7 +6312,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>333</v>
       </c>
@@ -6408,7 +6426,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>341</v>
       </c>
@@ -6520,7 +6538,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>347</v>
       </c>
@@ -6632,7 +6650,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>348</v>
       </c>
@@ -6746,7 +6764,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>349</v>
       </c>
@@ -6862,7 +6880,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>350</v>
       </c>
@@ -6978,7 +6996,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>352</v>
       </c>
@@ -7092,7 +7110,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>359</v>
       </c>
@@ -7206,7 +7224,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>369</v>
       </c>
@@ -7322,7 +7340,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>379</v>
       </c>
@@ -7436,7 +7454,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>388</v>
       </c>
@@ -7548,7 +7566,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>392</v>
       </c>
@@ -7664,7 +7682,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>399</v>
       </c>
@@ -7778,7 +7796,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>407</v>
       </c>
@@ -7892,7 +7910,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>415</v>
       </c>
@@ -8004,7 +8022,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>421</v>
       </c>
@@ -8118,7 +8136,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>431</v>
       </c>
@@ -8137,7 +8155,7 @@
         <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>77</v>
@@ -8232,7 +8250,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>437</v>
       </c>
@@ -8251,7 +8269,7 @@
         <v>86</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>77</v>
@@ -8346,7 +8364,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>445</v>
       </c>
@@ -8460,7 +8478,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>454</v>
       </c>
@@ -8479,7 +8497,7 @@
         <v>86</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>77</v>
@@ -8576,7 +8594,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>463</v>
       </c>
@@ -8690,7 +8708,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>471</v>
       </c>
@@ -8804,7 +8822,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>480</v>
       </c>
@@ -8918,7 +8936,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>485</v>
       </c>
@@ -9030,7 +9048,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>492</v>
       </c>
@@ -9049,7 +9067,7 @@
         <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>77</v>
@@ -9142,7 +9160,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>498</v>
       </c>
@@ -9256,7 +9274,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>506</v>
       </c>
@@ -9370,7 +9388,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>512</v>
       </c>
@@ -9482,7 +9500,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>513</v>
       </c>
@@ -9596,7 +9614,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>514</v>
       </c>
@@ -9712,7 +9730,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>519</v>
       </c>
@@ -9826,7 +9844,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>525</v>
       </c>
@@ -9942,7 +9960,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>531</v>
       </c>
@@ -10054,7 +10072,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>536</v>
       </c>
@@ -10168,7 +10186,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>542</v>
       </c>
@@ -10280,7 +10298,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
         <v>543</v>
       </c>
@@ -10394,7 +10412,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
         <v>544</v>
       </c>
@@ -10510,7 +10528,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
         <v>545</v>
       </c>
@@ -10626,7 +10644,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
         <v>552</v>
       </c>
@@ -10738,7 +10756,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
         <v>556</v>
       </c>
@@ -10757,7 +10775,7 @@
         <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>77</v>
@@ -10852,7 +10870,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
         <v>560</v>
       </c>
@@ -10964,7 +10982,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
         <v>561</v>
       </c>
@@ -11078,7 +11096,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
         <v>562</v>
       </c>
@@ -11194,7 +11212,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
         <v>563</v>
       </c>
@@ -11308,7 +11326,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
         <v>568</v>
       </c>
@@ -11420,7 +11438,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
         <v>569</v>
       </c>
@@ -11534,7 +11552,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
         <v>570</v>
       </c>
@@ -11650,7 +11668,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
         <v>571</v>
       </c>
@@ -11762,7 +11780,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
         <v>572</v>
       </c>
@@ -11876,7 +11894,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
         <v>573</v>
       </c>
@@ -11992,7 +12010,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
         <v>574</v>
       </c>
@@ -12106,7 +12124,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
         <v>575</v>
       </c>
@@ -12218,7 +12236,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
         <v>577</v>
       </c>
@@ -12332,7 +12350,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
         <v>578</v>
       </c>
@@ -12448,7 +12466,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
         <v>579</v>
       </c>
@@ -12564,7 +12582,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
         <v>581</v>
       </c>
@@ -12676,7 +12694,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
         <v>588</v>
       </c>
@@ -12793,6 +12811,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN93">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI92">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:19:29+00:00</t>
+    <t>2023-04-03T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:20:09+00:00</t>
+    <t>2023-04-03T10:41:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:41:47+00:00</t>
+    <t>2023-04-04T06:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T06:46:45+00:00</t>
+    <t>2023-04-04T06:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T06:47:21+00:00</t>
+    <t>2023-04-04T07:17:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T07:17:27+00:00</t>
+    <t>2023-04-04T08:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T08:23:07+00:00</t>
+    <t>2023-04-04T08:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T08:37:07+00:00</t>
+    <t>2023-04-04T09:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:08:50+00:00</t>
+    <t>2023-04-04T09:09:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:09:26+00:00</t>
+    <t>2023-04-04T09:19:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:19:23+00:00</t>
+    <t>2023-04-04T09:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:25:44+00:00</t>
+    <t>2023-04-04T10:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:05:29+00:00</t>
+    <t>2023-04-04T10:21:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:21:49+00:00</t>
+    <t>2023-04-04T10:30:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:30:43+00:00</t>
+    <t>2023-04-04T10:41:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:41:10+00:00</t>
+    <t>2023-04-04T10:41:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:41:37+00:00</t>
+    <t>2023-04-04T10:49:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:49:31+00:00</t>
+    <t>2023-04-04T13:12:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T13:12:12+00:00</t>
+    <t>2023-04-04T13:39:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T13:39:29+00:00</t>
+    <t>2023-04-17T11:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:49:04+00:00</t>
+    <t>2023-04-17T12:05:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:05:39+00:00</t>
+    <t>2023-04-17T12:49:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3390" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3392" uniqueCount="590">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:49:16+00:00</t>
+    <t>2023-05-26T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -1986,7 +1986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -2073,77 +2073,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>36</v>
       </c>
     </row>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:19+00:00</t>
+    <t>2023-05-26T12:35:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:50+00:00</t>
+    <t>2023-05-26T12:45:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:45:45+00:00</t>
+    <t>2023-05-26T12:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:47:23+00:00</t>
+    <t>2023-05-26T13:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:04:11+00:00</t>
+    <t>2023-05-26T13:05:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:05:32+00:00</t>
+    <t>2023-05-26T13:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:09:55+00:00</t>
+    <t>2023-05-26T14:47:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:47:38+00:00</t>
+    <t>2023-05-26T14:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:52:17+00:00</t>
+    <t>2023-05-26T14:59:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:59:52+00:00</t>
+    <t>2023-05-26T15:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:03:26+00:00</t>
+    <t>2023-05-26T15:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3392" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3392" uniqueCount="589">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:10:57+00:00</t>
+    <t>2023-05-29T05:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -474,14 +474,14 @@
     <t>The business identifier for this task.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:system}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
     <t>Slice based on the type of identifier.</t>
   </si>
   <si>
-    <t>openAtEnd</t>
+    <t>open</t>
   </si>
   <si>
     <t>Request.identifier, Event.identifier</t>
@@ -535,9 +535,6 @@
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -3774,10 +3771,10 @@
         <v>77</v>
       </c>
       <c r="AE14" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3806,10 +3803,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3835,16 +3832,16 @@
         <v>106</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3869,31 +3866,31 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3911,7 +3908,7 @@
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3922,10 +3919,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3948,19 +3945,19 @@
         <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3985,31 +3982,31 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4027,21 +4024,21 @@
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4150,10 +4147,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4232,10 +4229,10 @@
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4264,10 +4261,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4290,19 +4287,19 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4351,7 +4348,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4369,21 +4366,21 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>205</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4492,10 +4489,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4574,10 +4571,10 @@
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4606,10 +4603,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4635,16 +4632,16 @@
         <v>100</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4654,46 +4651,46 @@
         <v>77</v>
       </c>
       <c r="S22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4711,21 +4708,21 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>219</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4751,13 +4748,13 @@
         <v>157</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4807,7 +4804,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4825,21 +4822,21 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>227</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4865,14 +4862,14 @@
         <v>106</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4921,7 +4918,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4939,21 +4936,21 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>235</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4979,14 +4976,14 @@
         <v>157</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4996,46 +4993,46 @@
         <v>77</v>
       </c>
       <c r="S25" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5053,21 +5050,21 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>244</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5090,19 +5087,19 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -5151,7 +5148,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5169,21 +5166,21 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>254</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5209,16 +5206,16 @@
         <v>157</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -5228,46 +5225,46 @@
         <v>77</v>
       </c>
       <c r="S27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5285,21 +5282,21 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>264</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5325,65 +5322,65 @@
         <v>100</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T28" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="S28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T28" t="s" s="2">
+      <c r="U28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5401,21 +5398,21 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>275</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5441,13 +5438,13 @@
         <v>157</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5461,43 +5458,43 @@
         <v>77</v>
       </c>
       <c r="T29" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5515,21 +5512,21 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5552,13 +5549,13 @@
         <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5609,7 +5606,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5627,21 +5624,21 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>292</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5664,16 +5661,16 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5723,7 +5720,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5741,21 +5738,21 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>301</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5778,17 +5775,17 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5837,7 +5834,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5852,10 +5849,10 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5866,10 +5863,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5895,14 +5892,14 @@
         <v>100</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5951,7 +5948,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5966,10 +5963,10 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5980,10 +5977,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6006,13 +6003,13 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6063,7 +6060,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6078,10 +6075,10 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -6092,10 +6089,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6121,14 +6118,14 @@
         <v>144</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -6177,7 +6174,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6192,10 +6189,10 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -6206,10 +6203,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6232,19 +6229,19 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6293,7 +6290,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6308,10 +6305,10 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -6322,10 +6319,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6351,14 +6348,14 @@
         <v>106</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6383,13 +6380,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6407,7 +6404,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>86</v>
@@ -6422,13 +6419,13 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6436,10 +6433,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6462,16 +6459,16 @@
         <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6497,11 +6494,11 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6519,7 +6516,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6537,7 +6534,7 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -6548,10 +6545,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6660,10 +6657,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6742,10 +6739,10 @@
         <v>77</v>
       </c>
       <c r="AE40" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6774,10 +6771,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6800,19 +6797,19 @@
         <v>87</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6861,7 +6858,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6879,21 +6876,21 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>205</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6919,16 +6916,16 @@
         <v>157</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6938,7 +6935,7 @@
         <v>77</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>77</v>
@@ -6977,7 +6974,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6995,21 +6992,21 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>264</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7032,17 +7029,17 @@
         <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -7067,11 +7064,11 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="Y43" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="Y43" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="Z43" t="s" s="2">
         <v>77</v>
       </c>
@@ -7091,7 +7088,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7109,7 +7106,7 @@
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -7120,10 +7117,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7149,13 +7146,13 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7166,29 +7163,29 @@
         <v>77</v>
       </c>
       <c r="S44" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y44" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="T44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y44" t="s" s="2">
+      <c r="Z44" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>365</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
       </c>
@@ -7205,7 +7202,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>86</v>
@@ -7220,13 +7217,13 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -7234,10 +7231,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7263,48 +7260,48 @@
         <v>106</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q45" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="P45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q45" t="s" s="2">
+      <c r="R45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y45" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="R45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y45" t="s" s="2">
+      <c r="Z45" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>375</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
       </c>
@@ -7321,7 +7318,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7336,13 +7333,13 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -7350,10 +7347,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7376,16 +7373,16 @@
         <v>87</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7411,14 +7408,14 @@
         <v>77</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>384</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>77</v>
       </c>
@@ -7435,7 +7432,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7450,13 +7447,13 @@
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -7464,10 +7461,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7493,10 +7490,10 @@
         <v>157</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7547,7 +7544,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7565,7 +7562,7 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7576,10 +7573,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7602,19 +7599,19 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7663,7 +7660,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7681,10 +7678,10 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7692,14 +7689,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7718,17 +7715,17 @@
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7777,7 +7774,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7792,13 +7789,13 @@
         <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7806,10 +7803,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7832,17 +7829,17 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7891,7 +7888,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7906,13 +7903,13 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7920,10 +7917,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7946,13 +7943,13 @@
         <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8003,7 +8000,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8018,13 +8015,13 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AM51" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -8032,14 +8029,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8058,17 +8055,17 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8117,7 +8114,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8126,19 +8123,19 @@
         <v>86</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -8146,14 +8143,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8172,17 +8169,17 @@
         <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -8231,7 +8228,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8240,7 +8237,7 @@
         <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>98</v>
@@ -8249,7 +8246,7 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -8260,10 +8257,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8286,17 +8283,17 @@
         <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8345,7 +8342,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8360,13 +8357,13 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AM54" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8374,10 +8371,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8400,17 +8397,17 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8438,11 +8435,11 @@
         <v>110</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
       </c>
@@ -8459,7 +8456,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8474,13 +8471,13 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8488,14 +8485,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8514,19 +8511,19 @@
         <v>87</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8575,7 +8572,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8590,13 +8587,13 @@
         <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>462</v>
-      </c>
       <c r="AM56" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8604,10 +8601,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8630,17 +8627,17 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8689,7 +8686,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8704,13 +8701,13 @@
         <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AM57" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8718,10 +8715,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8744,16 +8741,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8779,10 +8776,10 @@
         <v>77</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="Z58" t="s" s="2">
         <v>77</v>
@@ -8803,7 +8800,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8818,24 +8815,24 @@
         <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AM58" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>479</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8858,16 +8855,16 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="M59" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8917,7 +8914,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8932,13 +8929,13 @@
         <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AL59" t="s" s="2">
-        <v>484</v>
-      </c>
       <c r="AM59" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -8946,10 +8943,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8972,13 +8969,13 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9029,7 +9026,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9044,24 +9041,24 @@
         <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>491</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9084,13 +9081,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9141,7 +9138,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9156,10 +9153,10 @@
         <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -9170,14 +9167,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9196,16 +9193,16 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9255,7 +9252,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9270,10 +9267,10 @@
         <v>98</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -9284,10 +9281,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9310,17 +9307,17 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9369,7 +9366,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9387,7 +9384,7 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -9398,10 +9395,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9510,10 +9507,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9595,7 +9592,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9624,14 +9621,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9653,10 +9650,10 @@
         <v>132</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>135</v>
@@ -9711,7 +9708,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9740,10 +9737,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9766,17 +9763,17 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -9825,7 +9822,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9843,7 +9840,7 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9854,10 +9851,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9880,19 +9877,19 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9941,7 +9938,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9959,7 +9956,7 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9970,10 +9967,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9996,13 +9993,13 @@
         <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10053,7 +10050,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10071,7 +10068,7 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -10082,14 +10079,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10108,17 +10105,17 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -10167,7 +10164,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10185,7 +10182,7 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -10196,10 +10193,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10308,10 +10305,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10393,7 +10390,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10422,14 +10419,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10451,10 +10448,10 @@
         <v>132</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>135</v>
@@ -10509,7 +10506,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10538,14 +10535,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10564,19 +10561,19 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -10601,10 +10598,10 @@
         <v>77</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Z74" t="s" s="2">
         <v>77</v>
@@ -10625,7 +10622,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>86</v>
@@ -10643,7 +10640,7 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -10654,10 +10651,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10680,13 +10677,13 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10737,7 +10734,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>86</v>
@@ -10755,7 +10752,7 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -10766,10 +10763,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10792,17 +10789,17 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -10851,7 +10848,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10869,7 +10866,7 @@
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10880,10 +10877,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10992,10 +10989,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11077,7 +11074,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11106,14 +11103,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11135,10 +11132,10 @@
         <v>132</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>135</v>
@@ -11193,7 +11190,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11222,14 +11219,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11248,17 +11245,17 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>77</v>
@@ -11283,10 +11280,10 @@
         <v>77</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="Z80" t="s" s="2">
         <v>77</v>
@@ -11307,7 +11304,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>86</v>
@@ -11325,7 +11322,7 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -11336,10 +11333,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11448,10 +11445,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11530,10 +11527,10 @@
         <v>77</v>
       </c>
       <c r="AE82" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11562,10 +11559,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11588,19 +11585,19 @@
         <v>87</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
@@ -11649,7 +11646,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11667,21 +11664,21 @@
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>205</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11790,10 +11787,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11872,10 +11869,10 @@
         <v>77</v>
       </c>
       <c r="AE85" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11904,10 +11901,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11933,16 +11930,16 @@
         <v>100</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>77</v>
@@ -11991,7 +11988,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12009,21 +12006,21 @@
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>219</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12049,13 +12046,13 @@
         <v>157</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12105,7 +12102,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12123,21 +12120,21 @@
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>227</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12163,14 +12160,14 @@
         <v>106</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>77</v>
@@ -12195,11 +12192,11 @@
         <v>77</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>77</v>
@@ -12217,7 +12214,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12235,21 +12232,21 @@
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>235</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12275,14 +12272,14 @@
         <v>157</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
@@ -12331,7 +12328,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12349,21 +12346,21 @@
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>244</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12386,19 +12383,19 @@
         <v>87</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="M90" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>77</v>
@@ -12447,7 +12444,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12465,21 +12462,21 @@
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>254</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12505,16 +12502,16 @@
         <v>157</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -12524,7 +12521,7 @@
         <v>77</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>77</v>
@@ -12563,7 +12560,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12581,21 +12578,21 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>264</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12618,17 +12615,17 @@
         <v>77</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>77</v>
@@ -12665,17 +12662,17 @@
         <v>77</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AC92" s="2"/>
       <c r="AD92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>86</v>
@@ -12693,7 +12690,7 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
@@ -12704,13 +12701,13 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C93" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>77</v>
@@ -12732,17 +12729,17 @@
         <v>77</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
@@ -12791,7 +12788,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>86</v>
@@ -12809,7 +12806,7 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-29T05:00:29+00:00</t>
+    <t>2023-05-29T05:09:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-12T13:14:32+00:00</t>
+    <t>2023-06-13T16:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:44:52+00:00</t>
+    <t>2023-06-13T16:48:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:48:27+00:00</t>
+    <t>2023-06-13T16:56:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:56:41+00:00</t>
+    <t>2023-06-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-20T13:48:39+00:00</t>
+    <t>2023-06-20T13:48:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-lab-task.xlsx
+++ b/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-20T13:48:52+00:00</t>
+    <t>2023-06-20T13:53:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
